--- a/save_brc_test.xlsx
+++ b/save_brc_test.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1\deep_sdy_v1.4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1\deep_sdy_v1.7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26CBA9D7-CE5E-4AF5-B239-A2B1FE9AA07B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB1629F-3EB1-42D2-A1EE-DAE3CA65BD20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4188" yWindow="1992" windowWidth="17628" windowHeight="9084" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1536" windowWidth="15360" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -358,10 +358,10 @@
         <v>1</v>
       </c>
       <c r="B1">
-        <v>50</v>
+        <v>2.0648714953349554</v>
       </c>
       <c r="C1">
-        <v>2.0184168691835529</v>
+        <v>1.7635461837815953</v>
       </c>
       <c r="D1">
         <v>1.8336375132693932</v>
